--- a/10. Sistemas de gestion empresarial/EmpleadosPorDepartamento.xlsx
+++ b/10. Sistemas de gestion empresarial/EmpleadosPorDepartamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheng\Desktop\2DAM\10. Sistemas de gestion empresarial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7586C9-8A02-401B-9EDF-069F17BB526B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81520432-4007-4A1F-BE86-93E9CC045B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,31 +228,35 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Horas extraordinarias de nuevos'!$A$3:$A$10</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas extraordinarias de nuevos'!$A$3:$A$10</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Horas extraordinarias de nuevos'!$A$4:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>     Administración / Administración</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>     Administración / Administración</c:v>
+                  <c:v>     Administración</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>     Administración</c:v>
+                  <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU.</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU.</c:v>
+                  <c:v>     Administración / Investigación y desarrollo</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>     Administración / Investigación y desarrollo</c:v>
+                  <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU. / Proyectos a largo plazo</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU. / Proyectos a largo plazo</c:v>
+                  <c:v>     Administración / Servicios profesionales</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>     Administración / Servicios profesionales</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>     Administración / Ventas</c:v>
                 </c:pt>
               </c:strCache>
@@ -260,32 +264,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Horas extraordinarias de nuevos'!$B$3:$B$10</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas extraordinarias de nuevos'!$B$3:$B$10</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Horas extraordinarias de nuevos'!$B$4:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
